--- a/ci-cd-merge-resolver/repoCollector/datasets/aws-sdk-java-v2.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/aws-sdk-java-v2.xlsx
@@ -44,43 +44,61 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>6c1f0b95bfb0b8815f435d8b5ce3967e94cd94c3</t>
+  </si>
+  <si>
     <t>4a7db6a609abe5fe716ab2ce6df7b67aa6e960ca</t>
   </si>
   <si>
+    <t>5bf9f20cb7e15568110a4bf4c8ac3cd378b2db31</t>
+  </si>
+  <si>
     <t>a57a1371df96ebb55f87213ee20996c7b7203174</t>
   </si>
   <si>
     <t>bbb2a963e658caf66cf3a426505de5b26ef434c2</t>
   </si>
   <si>
+    <t>07ca27cb12ea96e7a1b2a98fc6ba59326898101d</t>
+  </si>
+  <si>
+    <t>79643bcaaf12650937054cb3ac64df65d2d4e82b</t>
+  </si>
+  <si>
+    <t>b1cb504308485af5873c70972ccd38552031898c</t>
+  </si>
+  <si>
+    <t>477dc7c6268461522eb27f4f0ba0e951b2c5237c</t>
+  </si>
+  <si>
+    <t>3cdb4cd0d5e651e20b604c2188d9569f97b887e8</t>
+  </si>
+  <si>
+    <t>8e0ec002d7e210e781e7b1639437901f47a8e946</t>
+  </si>
+  <si>
     <t>20c88b24ff62fcee7eab7d8a9e3a08f981870a4b</t>
   </si>
   <si>
-    <t>477dc7c6268461522eb27f4f0ba0e951b2c5237c</t>
-  </si>
-  <si>
     <t>9c7c1e7a81743417cb0cdd8c1c6c195e01696eab</t>
   </si>
   <si>
-    <t>3cdb4cd0d5e651e20b604c2188d9569f97b887e8</t>
-  </si>
-  <si>
-    <t>8e0ec002d7e210e781e7b1639437901f47a8e946</t>
-  </si>
-  <si>
-    <t>07ca27cb12ea96e7a1b2a98fc6ba59326898101d</t>
-  </si>
-  <si>
-    <t>79643bcaaf12650937054cb3ac64df65d2d4e82b</t>
-  </si>
-  <si>
-    <t>b1cb504308485af5873c70972ccd38552031898c</t>
-  </si>
-  <si>
-    <t>6c1f0b95bfb0b8815f435d8b5ce3967e94cd94c3</t>
-  </si>
-  <si>
-    <t>5bf9f20cb7e15568110a4bf4c8ac3cd378b2db31</t>
+    <t>e888d95027efd5c19fac7b04c5426b45ebb57e81</t>
+  </si>
+  <si>
+    <t>f27862306ce41e42a5e921c75ffc756a01683734</t>
+  </si>
+  <si>
+    <t>5e56f118b734222f2203b7b43e418b2f7f1244ae</t>
+  </si>
+  <si>
+    <t>fa96f2735d1fda101ce9c15bdc5a7d49d76b1751</t>
+  </si>
+  <si>
+    <t>74c602f9158338ca8d1db4e24e140c2931090687</t>
+  </si>
+  <si>
+    <t>3cf77a2346fb40bf4a9f875f0412adcead1da295</t>
   </si>
   <si>
     <t>9273c3295e9095c21c04dc627d75a39ec58fd2e2</t>
@@ -90,24 +108,6 @@
   </si>
   <si>
     <t>41c3f18b9733ccb6a99a6cddc15700a2b13a794b</t>
-  </si>
-  <si>
-    <t>fa96f2735d1fda101ce9c15bdc5a7d49d76b1751</t>
-  </si>
-  <si>
-    <t>74c602f9158338ca8d1db4e24e140c2931090687</t>
-  </si>
-  <si>
-    <t>3cf77a2346fb40bf4a9f875f0412adcead1da295</t>
-  </si>
-  <si>
-    <t>e888d95027efd5c19fac7b04c5426b45ebb57e81</t>
-  </si>
-  <si>
-    <t>f27862306ce41e42a5e921c75ffc756a01683734</t>
-  </si>
-  <si>
-    <t>5e56f118b734222f2203b7b43e418b2f7f1244ae</t>
   </si>
 </sst>
 </file>
@@ -201,10 +201,10 @@
         <v>18.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -213,30 +213,30 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>8.44800090789795</v>
+        <v>13.318000793457031</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="s" s="0">
         <v>14</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -245,15 +245,15 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>8.14799976348877</v>
+        <v>12.263999938964844</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>16</v>
@@ -262,13 +262,13 @@
         <v>17</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -277,10 +277,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.14800000190734863</v>
+        <v>14.347000122070312</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -297,10 +297,10 @@
         <v>18.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>15.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -309,10 +309,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>9.284000396728516</v>
+        <v>14.845000267028809</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -320,7 +320,7 @@
         <v>21</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>22</v>
@@ -329,10 +329,10 @@
         <v>18.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -341,10 +341,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>7.61400032043457</v>
+        <v>15.03499984741211</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -361,10 +361,10 @@
         <v>12.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -373,10 +373,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>4.458000183105469</v>
+        <v>9.333999633789062</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -405,10 +405,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>2.8550000190734863</v>
+        <v>3.5370001792907715</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -425,10 +425,10 @@
         <v>12.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -437,10 +437,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>4.680999755859375</v>
+        <v>3.383000135421753</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
